--- a/portco-job-listings.xlsx
+++ b/portco-job-listings.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted Wagner\projects\portfolio-job-scraper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EC8F47-6476-46C8-A16A-D03EB99891A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53A77F8-70F3-4526-85C7-A5A92757D2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9617D107-92D9-4DF9-9F30-71F7090BD477}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -766,22 +764,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99C7A0F8-AD67-466E-8D1F-8F46C6373012}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E517555F-A116-4C12-B967-5BC4DE38857B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>